--- a/assets/excel/2026_4-2-1.xlsx
+++ b/assets/excel/2026_4-2-1.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A17ADF-4BB3-4A0F-A9FC-A1A68816EA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DF893-DAF0-4388-BFEE-23BEC2D2D38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F00CF707-31DB-41A0-9AE6-C8AE49075CB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -438,98 +435,98 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -548,498 +545,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="4-2-1_Download"/>
-      <sheetName val="CSV_Vorbereitung"/>
-      <sheetName val="CSV_Export"/>
-      <sheetName val="2021"/>
-      <sheetName val="2022"/>
-      <sheetName val="2023"/>
-      <sheetName val="2024"/>
-      <sheetName val="2025"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="14">
-          <cell r="D14">
-            <v>236.59</v>
-          </cell>
-          <cell r="E14">
-            <v>135.28</v>
-          </cell>
-          <cell r="F14">
-            <v>65.25</v>
-          </cell>
-          <cell r="G14">
-            <v>70.03</v>
-          </cell>
-          <cell r="H14">
-            <v>101.31</v>
-          </cell>
-          <cell r="I14">
-            <v>51.49</v>
-          </cell>
-          <cell r="J14">
-            <v>49.82</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>467.07</v>
-          </cell>
-          <cell r="E15">
-            <v>242.65</v>
-          </cell>
-          <cell r="F15">
-            <v>193.93</v>
-          </cell>
-          <cell r="G15">
-            <v>48.72</v>
-          </cell>
-          <cell r="H15">
-            <v>224.41</v>
-          </cell>
-          <cell r="I15">
-            <v>180.95</v>
-          </cell>
-          <cell r="J15">
-            <v>43.46</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>231.92</v>
-          </cell>
-          <cell r="E16">
-            <v>109.83</v>
-          </cell>
-          <cell r="F16">
-            <v>79.78</v>
-          </cell>
-          <cell r="G16">
-            <v>30.05</v>
-          </cell>
-          <cell r="H16">
-            <v>122.1</v>
-          </cell>
-          <cell r="I16">
-            <v>91.14</v>
-          </cell>
-          <cell r="J16">
-            <v>30.95</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>935.58</v>
-          </cell>
-          <cell r="E17">
-            <v>487.75</v>
-          </cell>
-          <cell r="F17">
-            <v>338.96</v>
-          </cell>
-          <cell r="G17">
-            <v>148.79</v>
-          </cell>
-          <cell r="H17">
-            <v>447.82</v>
-          </cell>
-          <cell r="I17">
-            <v>323.58</v>
-          </cell>
-          <cell r="J17">
-            <v>124.24</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="14">
-          <cell r="D14">
-            <v>254.56</v>
-          </cell>
-          <cell r="E14">
-            <v>139.59</v>
-          </cell>
-          <cell r="F14">
-            <v>68.11</v>
-          </cell>
-          <cell r="G14">
-            <v>71.48</v>
-          </cell>
-          <cell r="H14">
-            <v>114.98</v>
-          </cell>
-          <cell r="I14">
-            <v>58.08</v>
-          </cell>
-          <cell r="J14">
-            <v>56.9</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>445.45</v>
-          </cell>
-          <cell r="E15">
-            <v>233.74</v>
-          </cell>
-          <cell r="F15">
-            <v>188.05</v>
-          </cell>
-          <cell r="G15">
-            <v>45.69</v>
-          </cell>
-          <cell r="H15">
-            <v>211.71</v>
-          </cell>
-          <cell r="I15">
-            <v>170.67</v>
-          </cell>
-          <cell r="J15">
-            <v>41.04</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>246.45</v>
-          </cell>
-          <cell r="E16">
-            <v>115.77</v>
-          </cell>
-          <cell r="F16">
-            <v>81.93</v>
-          </cell>
-          <cell r="G16">
-            <v>33.840000000000003</v>
-          </cell>
-          <cell r="H16">
-            <v>130.68</v>
-          </cell>
-          <cell r="I16">
-            <v>95.99</v>
-          </cell>
-          <cell r="J16">
-            <v>34.69</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>946.46</v>
-          </cell>
-          <cell r="E17">
-            <v>489.1</v>
-          </cell>
-          <cell r="F17">
-            <v>338.09</v>
-          </cell>
-          <cell r="G17">
-            <v>151.01</v>
-          </cell>
-          <cell r="H17">
-            <v>457.37</v>
-          </cell>
-          <cell r="I17">
-            <v>324.74</v>
-          </cell>
-          <cell r="J17">
-            <v>132.63</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="14">
-          <cell r="D14">
-            <v>250.2</v>
-          </cell>
-          <cell r="E14">
-            <v>136.21</v>
-          </cell>
-          <cell r="F14">
-            <v>62.12</v>
-          </cell>
-          <cell r="G14">
-            <v>74.09</v>
-          </cell>
-          <cell r="H14">
-            <v>113.99</v>
-          </cell>
-          <cell r="I14">
-            <v>55.29</v>
-          </cell>
-          <cell r="J14">
-            <v>58.7</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>443.84</v>
-          </cell>
-          <cell r="E15">
-            <v>240.45</v>
-          </cell>
-          <cell r="F15">
-            <v>195.4</v>
-          </cell>
-          <cell r="G15">
-            <v>45.06</v>
-          </cell>
-          <cell r="H15">
-            <v>203.39</v>
-          </cell>
-          <cell r="I15">
-            <v>164.15</v>
-          </cell>
-          <cell r="J15">
-            <v>39.229999999999997</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>261</v>
-          </cell>
-          <cell r="E16">
-            <v>119.99</v>
-          </cell>
-          <cell r="F16">
-            <v>87.78</v>
-          </cell>
-          <cell r="G16">
-            <v>32.22</v>
-          </cell>
-          <cell r="H16">
-            <v>141.01</v>
-          </cell>
-          <cell r="I16">
-            <v>104.07</v>
-          </cell>
-          <cell r="J16">
-            <v>36.94</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>955.04</v>
-          </cell>
-          <cell r="E17">
-            <v>496.65</v>
-          </cell>
-          <cell r="F17">
-            <v>345.29</v>
-          </cell>
-          <cell r="G17">
-            <v>151.36000000000001</v>
-          </cell>
-          <cell r="H17">
-            <v>458.39</v>
-          </cell>
-          <cell r="I17">
-            <v>323.52</v>
-          </cell>
-          <cell r="J17">
-            <v>134.87</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="14">
-          <cell r="D14">
-            <v>240.37</v>
-          </cell>
-          <cell r="E14">
-            <v>136.41</v>
-          </cell>
-          <cell r="F14">
-            <v>57.64</v>
-          </cell>
-          <cell r="G14">
-            <v>78.78</v>
-          </cell>
-          <cell r="H14">
-            <v>103.95</v>
-          </cell>
-          <cell r="I14">
-            <v>47.45</v>
-          </cell>
-          <cell r="J14">
-            <v>56.5</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>452.11</v>
-          </cell>
-          <cell r="E15">
-            <v>241.4</v>
-          </cell>
-          <cell r="F15">
-            <v>192.17</v>
-          </cell>
-          <cell r="G15">
-            <v>49.23</v>
-          </cell>
-          <cell r="H15">
-            <v>210.71</v>
-          </cell>
-          <cell r="I15">
-            <v>164.17</v>
-          </cell>
-          <cell r="J15">
-            <v>46.54</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>273.95</v>
-          </cell>
-          <cell r="E16">
-            <v>123.85</v>
-          </cell>
-          <cell r="F16">
-            <v>91.26</v>
-          </cell>
-          <cell r="G16">
-            <v>32.590000000000003</v>
-          </cell>
-          <cell r="H16">
-            <v>150.1</v>
-          </cell>
-          <cell r="I16">
-            <v>109.79</v>
-          </cell>
-          <cell r="J16">
-            <v>40.31</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>966.43</v>
-          </cell>
-          <cell r="E17">
-            <v>501.66</v>
-          </cell>
-          <cell r="F17">
-            <v>341.07</v>
-          </cell>
-          <cell r="G17">
-            <v>160.6</v>
-          </cell>
-          <cell r="H17">
-            <v>464.76</v>
-          </cell>
-          <cell r="I17">
-            <v>321.41000000000003</v>
-          </cell>
-          <cell r="J17">
-            <v>143.35</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="14">
-          <cell r="D14">
-            <v>202.95</v>
-          </cell>
-          <cell r="E14">
-            <v>120.18</v>
-          </cell>
-          <cell r="F14">
-            <v>45.63</v>
-          </cell>
-          <cell r="G14">
-            <v>74.55</v>
-          </cell>
-          <cell r="H14">
-            <v>82.77</v>
-          </cell>
-          <cell r="I14">
-            <v>33.64</v>
-          </cell>
-          <cell r="J14">
-            <v>49.13</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="D15">
-            <v>466.77</v>
-          </cell>
-          <cell r="E15">
-            <v>247.41</v>
-          </cell>
-          <cell r="F15">
-            <v>193.2</v>
-          </cell>
-          <cell r="G15">
-            <v>54.2</v>
-          </cell>
-          <cell r="H15">
-            <v>219.36</v>
-          </cell>
-          <cell r="I15">
-            <v>169.95</v>
-          </cell>
-          <cell r="J15">
-            <v>49.41</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="D16">
-            <v>280.06</v>
-          </cell>
-          <cell r="E16">
-            <v>128.9</v>
-          </cell>
-          <cell r="F16">
-            <v>91.88</v>
-          </cell>
-          <cell r="G16">
-            <v>37.020000000000003</v>
-          </cell>
-          <cell r="H16">
-            <v>151.16</v>
-          </cell>
-          <cell r="I16">
-            <v>106.91</v>
-          </cell>
-          <cell r="J16">
-            <v>44.25</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>949.78</v>
-          </cell>
-          <cell r="E17">
-            <v>496.49</v>
-          </cell>
-          <cell r="F17">
-            <v>330.72</v>
-          </cell>
-          <cell r="G17">
-            <v>165.77</v>
-          </cell>
-          <cell r="H17">
-            <v>453.29</v>
-          </cell>
-          <cell r="I17">
-            <v>310.5</v>
-          </cell>
-          <cell r="J17">
-            <v>142.80000000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1392,817 +897,682 @@
       <c r="J5" s="7"/>
     </row>
     <row r="6" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
     </row>
     <row r="7" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="15" t="s">
+      <c r="E7" s="31"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="16"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="37"/>
     </row>
     <row r="8" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="11"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="13" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="15" t="s">
+      <c r="H8" s="31"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="37"/>
     </row>
     <row r="9" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="11"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="37"/>
     </row>
     <row r="10" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="11"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="23" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="37"/>
     </row>
     <row r="12" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="28">
+      <c r="B12" s="11">
         <v>1</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="11">
         <v>2</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="11">
         <v>3</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="11">
         <v>4</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="11">
         <v>5</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="11">
         <v>6</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="11">
         <v>7</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="11">
         <v>8</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="11">
         <v>9</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="11">
         <v>10</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="11">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="11">
         <v>2025</v>
       </c>
       <c r="D13" s="1">
-        <f>'[1]2025'!D14/'[1]2025'!D17*100</f>
         <v>21.36810629830066</v>
       </c>
       <c r="E13" s="1">
-        <f>'[1]2025'!E14/'[1]2025'!E17*100</f>
         <v>24.205925597695828</v>
       </c>
       <c r="F13" s="1">
-        <f>'[1]2025'!H14/'[1]2025'!H17*100</f>
         <v>18.259833660570493</v>
       </c>
       <c r="G13" s="1">
-        <f>('[1]2025'!G14+'[1]2025'!J14)/('[1]2025'!$G$17+'[1]2025'!$J$17)*100</f>
         <v>40.08166704475483</v>
       </c>
       <c r="H13" s="1">
-        <f>'[1]2025'!G14/'[1]2025'!$G$17*100</f>
         <v>44.971949086083121</v>
       </c>
       <c r="I13" s="1">
-        <f>'[1]2025'!J14/'[1]2025'!$J$17*100</f>
         <v>34.404761904761905</v>
       </c>
       <c r="J13" s="1">
-        <f>('[1]2025'!F14+'[1]2025'!I14)/('[1]2025'!$F$17+'[1]2025'!$I$17)*100</f>
         <v>12.362371728891802</v>
       </c>
       <c r="K13" s="1">
-        <f>'[1]2025'!F14/'[1]2025'!$F$17*100</f>
         <v>13.797169811320753</v>
       </c>
       <c r="L13" s="1">
-        <f>'[1]2025'!I14/'[1]2025'!$I$17*100</f>
         <v>10.8341384863124</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="11">
         <v>2025</v>
       </c>
       <c r="D14" s="1">
-        <f>'[1]2025'!D15/'[1]2025'!D17*100</f>
         <v>49.145065172987429</v>
       </c>
       <c r="E14" s="1">
-        <f>'[1]2025'!E15/'[1]2025'!E17*100</f>
         <v>49.831819371991379</v>
       </c>
       <c r="F14" s="1">
-        <f>'[1]2025'!H15/'[1]2025'!H17*100</f>
         <v>48.392861082309338</v>
       </c>
       <c r="G14" s="1">
-        <f>('[1]2025'!G15+'[1]2025'!J15)/('[1]2025'!$G$17+'[1]2025'!$J$17)*100</f>
         <v>33.577470266066037</v>
       </c>
       <c r="H14" s="1">
-        <f>'[1]2025'!G15/'[1]2025'!$G$17*100</f>
         <v>32.695903963322678</v>
       </c>
       <c r="I14" s="1">
-        <f>'[1]2025'!J15/'[1]2025'!$J$17*100</f>
         <v>34.600840336134446</v>
       </c>
       <c r="J14" s="1">
-        <f>('[1]2025'!F15+'[1]2025'!I15)/('[1]2025'!$F$17+'[1]2025'!$I$17)*100</f>
         <v>56.634228501918216</v>
       </c>
       <c r="K14" s="1">
-        <f>'[1]2025'!F15/'[1]2025'!$F$17*100</f>
         <v>58.41799709724237</v>
       </c>
       <c r="L14" s="1">
-        <f>'[1]2025'!I15/'[1]2025'!$I$17*100</f>
         <v>54.734299516908216</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="11">
         <v>2025</v>
       </c>
       <c r="D15" s="1">
-        <f>'[1]2025'!D16/'[1]2025'!D17*100</f>
         <v>29.486828528711911</v>
       </c>
       <c r="E15" s="1">
-        <f>'[1]2025'!E16/'[1]2025'!E17*100</f>
         <v>25.962255030312797</v>
       </c>
       <c r="F15" s="1">
-        <f>'[1]2025'!H16/'[1]2025'!H17*100</f>
         <v>33.347305257120162</v>
       </c>
       <c r="G15" s="1">
-        <f>('[1]2025'!G16+'[1]2025'!J16)/('[1]2025'!$G$17+'[1]2025'!$J$17)*100</f>
         <v>26.337621933434875</v>
       </c>
       <c r="H15" s="1">
-        <f>'[1]2025'!G16/'[1]2025'!$G$17*100</f>
         <v>22.332146950594197</v>
       </c>
       <c r="I15" s="1">
-        <f>'[1]2025'!J16/'[1]2025'!$J$17*100</f>
         <v>30.987394957983188</v>
       </c>
       <c r="J15" s="1">
-        <f>('[1]2025'!F16+'[1]2025'!I16)/('[1]2025'!$F$17+'[1]2025'!$I$17)*100</f>
         <v>31.001840242038615</v>
       </c>
       <c r="K15" s="1">
-        <f>'[1]2025'!F16/'[1]2025'!$F$17*100</f>
         <v>27.781809385582967</v>
       </c>
       <c r="L15" s="1">
-        <f>'[1]2025'!I16/'[1]2025'!$I$17*100</f>
         <v>34.431561996779386</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="11">
         <v>2024</v>
       </c>
       <c r="D16" s="1">
-        <f>'[1]2024'!D14/'[1]2024'!D17*100</f>
         <v>24.871951408793187</v>
       </c>
       <c r="E16" s="1">
-        <f>'[1]2024'!E14/'[1]2024'!E17*100</f>
         <v>27.191723478052864</v>
       </c>
       <c r="F16" s="1">
-        <f>'[1]2024'!H14/'[1]2024'!H17*100</f>
         <v>22.366382649109219</v>
       </c>
       <c r="G16" s="1">
-        <f>('[1]2024'!G14+'[1]2024'!J14)/('[1]2024'!$G$17+'[1]2024'!$J$17)*100</f>
         <v>44.507320282941279</v>
       </c>
       <c r="H16" s="1">
-        <f>'[1]2024'!G14/'[1]2024'!$G$17*100</f>
         <v>49.053549190535492</v>
       </c>
       <c r="I16" s="1">
-        <f>'[1]2024'!J14/'[1]2024'!$J$17*100</f>
         <v>39.414021625392401</v>
       </c>
       <c r="J16" s="1">
-        <f>('[1]2024'!F14+'[1]2024'!I14)/('[1]2024'!$F$17+'[1]2024'!$I$17)*100</f>
         <v>15.86312039608743</v>
       </c>
       <c r="K16" s="1">
-        <f>'[1]2024'!F14/'[1]2024'!$F$17*100</f>
         <v>16.899756648195385</v>
       </c>
       <c r="L16" s="1">
-        <f>'[1]2024'!I14/'[1]2024'!$I$17*100</f>
         <v>14.763075199900438</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="11">
         <v>2024</v>
       </c>
       <c r="D17" s="1">
-        <f>'[1]2024'!D15/'[1]2024'!D17*100</f>
         <v>46.781453390312805</v>
       </c>
       <c r="E17" s="1">
-        <f>'[1]2024'!E15/'[1]2024'!E17*100</f>
         <v>48.120240800542199</v>
       </c>
       <c r="F17" s="1">
-        <f>'[1]2024'!H15/'[1]2024'!H17*100</f>
         <v>45.337378431878825</v>
       </c>
       <c r="G17" s="1">
-        <f>('[1]2024'!G15+'[1]2024'!J15)/('[1]2024'!$G$17+'[1]2024'!$J$17)*100</f>
         <v>31.50847178812305</v>
       </c>
       <c r="H17" s="1">
-        <f>'[1]2024'!G15/'[1]2024'!$G$17*100</f>
         <v>30.653798256537986</v>
       </c>
       <c r="I17" s="1">
-        <f>'[1]2024'!J15/'[1]2024'!$J$17*100</f>
         <v>32.465992326473661</v>
       </c>
       <c r="J17" s="1">
-        <f>('[1]2024'!F15+'[1]2024'!I15)/('[1]2024'!$F$17+'[1]2024'!$I$17)*100</f>
         <v>53.788793623958455</v>
       </c>
       <c r="K17" s="1">
-        <f>'[1]2024'!F15/'[1]2024'!$F$17*100</f>
         <v>56.343272641979645</v>
       </c>
       <c r="L17" s="1">
-        <f>'[1]2024'!I15/'[1]2024'!$I$17*100</f>
         <v>51.078062288043299</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="11">
         <v>2024</v>
       </c>
       <c r="D18" s="1">
-        <f>'[1]2024'!D16/'[1]2024'!D17*100</f>
         <v>28.346595200894015</v>
       </c>
       <c r="E18" s="1">
-        <f>'[1]2024'!E16/'[1]2024'!E17*100</f>
         <v>24.688035721404933</v>
       </c>
       <c r="F18" s="1">
-        <f>'[1]2024'!H16/'[1]2024'!H17*100</f>
         <v>32.296238919011962</v>
       </c>
       <c r="G18" s="1">
-        <f>('[1]2024'!G16+'[1]2024'!J16)/('[1]2024'!$G$17+'[1]2024'!$J$17)*100</f>
         <v>23.984207928935682</v>
       </c>
       <c r="H18" s="1">
-        <f>'[1]2024'!G16/'[1]2024'!$G$17*100</f>
         <v>20.29265255292653</v>
       </c>
       <c r="I18" s="1">
-        <f>'[1]2024'!J16/'[1]2024'!$J$17*100</f>
         <v>28.119986048133939</v>
       </c>
       <c r="J18" s="1">
-        <f>('[1]2024'!F16+'[1]2024'!I16)/('[1]2024'!$F$17+'[1]2024'!$I$17)*100</f>
         <v>30.348085979954114</v>
       </c>
       <c r="K18" s="1">
-        <f>'[1]2024'!F16/'[1]2024'!$F$17*100</f>
         <v>26.756970709824962</v>
       </c>
       <c r="L18" s="1">
-        <f>'[1]2024'!I16/'[1]2024'!$I$17*100</f>
         <v>34.158862512056253</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="11">
         <v>2023</v>
       </c>
       <c r="D19" s="1">
-        <f>'[1]2023'!D14/'[1]2023'!D17*100</f>
         <v>26.197855587200536</v>
       </c>
       <c r="E19" s="1">
-        <f>'[1]2023'!E14/'[1]2023'!E17*100</f>
         <v>27.425752542031617</v>
       </c>
       <c r="F19" s="1">
-        <f>'[1]2023'!H14/'[1]2023'!H17*100</f>
         <v>24.867470930866727</v>
       </c>
       <c r="G19" s="1">
-        <f>('[1]2023'!G14+'[1]2023'!J14)/('[1]2023'!$G$17+'[1]2023'!$J$17)*100</f>
         <v>46.392761066275376</v>
       </c>
       <c r="H19" s="1">
-        <f>'[1]2023'!G14/'[1]2023'!$G$17*100</f>
         <v>48.949524312896401</v>
       </c>
       <c r="I19" s="1">
-        <f>'[1]2023'!J14/'[1]2023'!$J$17*100</f>
         <v>43.523392896863648</v>
       </c>
       <c r="J19" s="1">
-        <f>('[1]2023'!F14+'[1]2023'!I14)/('[1]2023'!$F$17+'[1]2023'!$I$17)*100</f>
         <v>17.555060480555014</v>
       </c>
       <c r="K19" s="1">
-        <f>'[1]2023'!F14/'[1]2023'!$F$17*100</f>
         <v>17.990674505488137</v>
       </c>
       <c r="L19" s="1">
-        <f>'[1]2023'!I14/'[1]2023'!$I$17*100</f>
         <v>17.090133531157271</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="11">
         <v>2023</v>
       </c>
       <c r="D20" s="1">
-        <f>'[1]2023'!D15/'[1]2023'!D17*100</f>
         <v>46.473446138381632</v>
       </c>
       <c r="E20" s="1">
-        <f>'[1]2023'!E15/'[1]2023'!E17*100</f>
         <v>48.414376321353068</v>
       </c>
       <c r="F20" s="1">
-        <f>'[1]2023'!H15/'[1]2023'!H17*100</f>
         <v>44.370514190972749</v>
       </c>
       <c r="G20" s="1">
-        <f>('[1]2023'!G15+'[1]2023'!J15)/('[1]2023'!$G$17+'[1]2023'!$J$17)*100</f>
         <v>29.448345735946614</v>
       </c>
       <c r="H20" s="1">
-        <f>'[1]2023'!G15/'[1]2023'!$G$17*100</f>
         <v>29.770084566596193</v>
       </c>
       <c r="I20" s="1">
-        <f>'[1]2023'!J15/'[1]2023'!$J$17*100</f>
         <v>29.08726922221398</v>
       </c>
       <c r="J20" s="1">
-        <f>('[1]2023'!F15+'[1]2023'!I15)/('[1]2023'!$F$17+'[1]2023'!$I$17)*100</f>
         <v>53.759662684469433</v>
       </c>
       <c r="K20" s="1">
-        <f>'[1]2023'!F15/'[1]2023'!$F$17*100</f>
         <v>56.590112658924383</v>
       </c>
       <c r="L20" s="1">
-        <f>'[1]2023'!I15/'[1]2023'!$I$17*100</f>
         <v>50.738748763600405</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="11">
         <v>2023</v>
       </c>
       <c r="D21" s="1">
-        <f>'[1]2023'!D16/'[1]2023'!D17*100</f>
         <v>27.328698274417828</v>
       </c>
       <c r="E21" s="1">
-        <f>'[1]2023'!E16/'[1]2023'!E17*100</f>
         <v>24.159871136615322</v>
       </c>
       <c r="F21" s="1">
-        <f>'[1]2023'!H16/'[1]2023'!H17*100</f>
         <v>30.762014878160514</v>
       </c>
       <c r="G21" s="1">
-        <f>('[1]2023'!G16+'[1]2023'!J16)/('[1]2023'!$G$17+'[1]2023'!$J$17)*100</f>
         <v>24.16238689166055</v>
       </c>
       <c r="H21" s="1">
-        <f>'[1]2023'!G16/'[1]2023'!$G$17*100</f>
         <v>21.286997885835092</v>
       </c>
       <c r="I21" s="1">
-        <f>'[1]2023'!J16/'[1]2023'!$J$17*100</f>
         <v>27.389337880922366</v>
       </c>
       <c r="J21" s="1">
-        <f>('[1]2023'!F16+'[1]2023'!I16)/('[1]2023'!$F$17+'[1]2023'!$I$17)*100</f>
         <v>28.685276834975554</v>
       </c>
       <c r="K21" s="1">
-        <f>'[1]2023'!F16/'[1]2023'!$F$17*100</f>
         <v>25.422108951895506</v>
       </c>
       <c r="L21" s="1">
-        <f>'[1]2023'!I16/'[1]2023'!$I$17*100</f>
         <v>32.168026706231458</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="11">
         <v>2022</v>
       </c>
       <c r="D22" s="1">
-        <f>'[1]2022'!D14/'[1]2022'!D17*100</f>
         <v>26.896012509773261</v>
       </c>
       <c r="E22" s="1">
-        <f>'[1]2022'!E14/'[1]2022'!E17*100</f>
         <v>28.540175833162952</v>
       </c>
       <c r="F22" s="1">
-        <f>'[1]2022'!H14/'[1]2022'!H17*100</f>
         <v>25.13938386864027</v>
       </c>
       <c r="G22" s="1">
-        <f>('[1]2022'!G14+'[1]2022'!J14)/('[1]2022'!$G$17+'[1]2022'!$J$17)*100</f>
         <v>45.261599210266532</v>
       </c>
       <c r="H22" s="1">
-        <f>'[1]2022'!G14/'[1]2022'!$G$17*100</f>
         <v>47.334613601748231</v>
       </c>
       <c r="I22" s="1">
-        <f>'[1]2022'!J14/'[1]2022'!$J$17*100</f>
         <v>42.901304380607705</v>
       </c>
       <c r="J22" s="1">
-        <f>('[1]2022'!F14+'[1]2022'!I14)/('[1]2022'!$F$17+'[1]2022'!$I$17)*100</f>
         <v>19.038064058657575</v>
       </c>
       <c r="K22" s="1">
-        <f>'[1]2022'!F14/'[1]2022'!$F$17*100</f>
         <v>20.145523381348163</v>
       </c>
       <c r="L22" s="1">
-        <f>'[1]2022'!I14/'[1]2022'!$I$17*100</f>
         <v>17.885077292603313</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="11">
         <v>2022</v>
       </c>
       <c r="D23" s="1">
-        <f>'[1]2022'!D15/'[1]2022'!D17*100</f>
         <v>47.064852186040611</v>
       </c>
       <c r="E23" s="1">
-        <f>'[1]2022'!E15/'[1]2022'!E17*100</f>
         <v>47.78981803312206</v>
       </c>
       <c r="F23" s="1">
-        <f>'[1]2022'!H15/'[1]2022'!H17*100</f>
         <v>46.288562870323808</v>
       </c>
       <c r="G23" s="1">
-        <f>('[1]2022'!G15+'[1]2022'!J15)/('[1]2022'!$G$17+'[1]2022'!$J$17)*100</f>
         <v>30.577492596248764</v>
       </c>
       <c r="H23" s="1">
-        <f>'[1]2022'!G15/'[1]2022'!$G$17*100</f>
         <v>30.256274418912653</v>
       </c>
       <c r="I23" s="1">
-        <f>'[1]2022'!J15/'[1]2022'!$J$17*100</f>
         <v>30.943225514589461</v>
       </c>
       <c r="J23" s="1">
-        <f>('[1]2022'!F15+'[1]2022'!I15)/('[1]2022'!$F$17+'[1]2022'!$I$17)*100</f>
         <v>54.119457477784664</v>
       </c>
       <c r="K23" s="1">
-        <f>'[1]2022'!F15/'[1]2022'!$F$17*100</f>
         <v>55.621284273418325</v>
       </c>
       <c r="L23" s="1">
-        <f>'[1]2022'!I15/'[1]2022'!$I$17*100</f>
         <v>52.555890866539379</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="11">
         <v>2022</v>
       </c>
       <c r="D24" s="1">
-        <f>'[1]2022'!D16/'[1]2022'!D17*100</f>
         <v>26.039135304186122</v>
       </c>
       <c r="E24" s="1">
-        <f>'[1]2022'!E16/'[1]2022'!E17*100</f>
         <v>23.670006133714985</v>
       </c>
       <c r="F24" s="1">
-        <f>'[1]2022'!H16/'[1]2022'!H17*100</f>
         <v>28.572053261035922</v>
       </c>
       <c r="G24" s="1">
-        <f>('[1]2022'!G16+'[1]2022'!J16)/('[1]2022'!$G$17+'[1]2022'!$J$17)*100</f>
         <v>24.160908193484701</v>
       </c>
       <c r="H24" s="1">
-        <f>'[1]2022'!G16/'[1]2022'!$G$17*100</f>
         <v>22.409111979339119</v>
       </c>
       <c r="I24" s="1">
-        <f>'[1]2022'!J16/'[1]2022'!$J$17*100</f>
         <v>26.155470104802838</v>
       </c>
       <c r="J24" s="1">
-        <f>('[1]2022'!F16+'[1]2022'!I16)/('[1]2022'!$F$17+'[1]2022'!$I$17)*100</f>
         <v>26.842478463557779</v>
       </c>
       <c r="K24" s="1">
-        <f>'[1]2022'!F16/'[1]2022'!$F$17*100</f>
         <v>24.233192345233519</v>
       </c>
       <c r="L24" s="1">
-        <f>'[1]2022'!I16/'[1]2022'!$I$17*100</f>
         <v>29.559031840857298</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="11">
         <v>2021</v>
       </c>
       <c r="D25" s="1">
-        <f>'[1]2021'!D14/'[1]2021'!D17*100</f>
         <v>25.288056606596975</v>
       </c>
       <c r="E25" s="1">
-        <f>'[1]2021'!E14/'[1]2021'!E17*100</f>
         <v>27.735520246027679</v>
       </c>
       <c r="F25" s="1">
-        <f>'[1]2021'!H14/'[1]2021'!H17*100</f>
         <v>22.622928855343666</v>
       </c>
       <c r="G25" s="1">
-        <f>('[1]2021'!G14+'[1]2021'!J14)/('[1]2021'!$G$17+'[1]2021'!$J$17)*100</f>
         <v>43.896275134600593</v>
       </c>
       <c r="H25" s="1">
-        <f>'[1]2021'!G14/'[1]2021'!$G$17*100</f>
         <v>47.066335103165542</v>
       </c>
       <c r="I25" s="1">
-        <f>'[1]2021'!J14/'[1]2021'!$J$17*100</f>
         <v>40.099806825499037</v>
       </c>
       <c r="J25" s="1">
-        <f>('[1]2021'!F14+'[1]2021'!I14)/('[1]2021'!$F$17+'[1]2021'!$I$17)*100</f>
         <v>17.620068222296016</v>
       </c>
       <c r="K25" s="1">
-        <f>'[1]2021'!F14/'[1]2021'!$F$17*100</f>
         <v>19.250059004012275</v>
       </c>
       <c r="L25" s="1">
-        <f>'[1]2021'!I14/'[1]2021'!$I$17*100</f>
         <v>15.912602756659869</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="11">
         <v>2021</v>
       </c>
       <c r="D26" s="1">
-        <f>'[1]2021'!D15/'[1]2021'!D17*100</f>
         <v>49.923042390816391</v>
       </c>
       <c r="E26" s="1">
-        <f>'[1]2021'!E15/'[1]2021'!E17*100</f>
         <v>49.748846745258838</v>
       </c>
       <c r="F26" s="1">
-        <f>'[1]2021'!H15/'[1]2021'!H17*100</f>
         <v>50.11165200303693</v>
       </c>
       <c r="G26" s="1">
-        <f>('[1]2021'!G15+'[1]2021'!J15)/('[1]2021'!$G$17+'[1]2021'!$J$17)*100</f>
         <v>33.761857671318175</v>
       </c>
       <c r="H26" s="1">
-        <f>'[1]2021'!G15/'[1]2021'!$G$17*100</f>
         <v>32.744136030647219</v>
       </c>
       <c r="I26" s="1">
-        <f>'[1]2021'!J15/'[1]2021'!$J$17*100</f>
         <v>34.980682549903413</v>
       </c>
       <c r="J26" s="1">
-        <f>('[1]2021'!F15+'[1]2021'!I15)/('[1]2021'!$F$17+'[1]2021'!$I$17)*100</f>
         <v>56.582244090922821</v>
       </c>
       <c r="K26" s="1">
-        <f>'[1]2021'!F15/'[1]2021'!$F$17*100</f>
         <v>57.213240500354033</v>
       </c>
       <c r="L26" s="1">
-        <f>'[1]2021'!I15/'[1]2021'!$I$17*100</f>
         <v>55.921255949069781</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="11">
         <v>2021</v>
       </c>
       <c r="D27" s="1">
-        <f>'[1]2021'!D16/'[1]2021'!D17*100</f>
         <v>24.788901002586627</v>
       </c>
       <c r="E27" s="1">
-        <f>'[1]2021'!E16/'[1]2021'!E17*100</f>
         <v>22.517683239364427</v>
       </c>
       <c r="F27" s="1">
-        <f>'[1]2021'!H16/'[1]2021'!H17*100</f>
         <v>27.2654191416194</v>
       </c>
       <c r="G27" s="1">
-        <f>('[1]2021'!G16+'[1]2021'!J16)/('[1]2021'!$G$17+'[1]2021'!$J$17)*100</f>
         <v>22.341867194081239</v>
       </c>
       <c r="H27" s="1">
-        <f>'[1]2021'!G16/'[1]2021'!$G$17*100</f>
         <v>20.196249747966935</v>
       </c>
       <c r="I27" s="1">
-        <f>'[1]2021'!J16/'[1]2021'!$J$17*100</f>
         <v>24.911461687057308</v>
       </c>
       <c r="J27" s="1">
-        <f>('[1]2021'!F16+'[1]2021'!I16)/('[1]2021'!$F$17+'[1]2021'!$I$17)*100</f>
         <v>25.797687686781178</v>
       </c>
       <c r="K27" s="1">
-        <f>'[1]2021'!F16/'[1]2021'!$F$17*100</f>
         <v>23.536700495633706</v>
       </c>
       <c r="L27" s="1">
-        <f>'[1]2021'!I16/'[1]2021'!$I$17*100</f>
         <v>28.166141294270354</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="11">
         <v>2019</v>
       </c>
       <c r="D28" s="1">
@@ -2234,10 +1604,10 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="11">
         <v>2019</v>
       </c>
       <c r="D29" s="1">
@@ -2269,10 +1639,10 @@
       </c>
     </row>
     <row r="30" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="11">
         <v>2019</v>
       </c>
       <c r="D30" s="1">
@@ -2304,10 +1674,10 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="14">
         <v>2018</v>
       </c>
       <c r="D31" s="1">
@@ -2339,10 +1709,10 @@
       </c>
     </row>
     <row r="32" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="15">
         <v>2018</v>
       </c>
       <c r="D32" s="1">
@@ -2374,10 +1744,10 @@
       </c>
     </row>
     <row r="33" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="14">
         <v>2018</v>
       </c>
       <c r="D33" s="1">
@@ -2409,10 +1779,10 @@
       </c>
     </row>
     <row r="34" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="14">
         <v>2017</v>
       </c>
       <c r="D34" s="1">
@@ -2444,10 +1814,10 @@
       </c>
     </row>
     <row r="35" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="14">
         <v>2017</v>
       </c>
       <c r="D35" s="1">
@@ -2479,10 +1849,10 @@
       </c>
     </row>
     <row r="36" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="14">
         <v>2017</v>
       </c>
       <c r="D36" s="1">
@@ -2514,10 +1884,10 @@
       </c>
     </row>
     <row r="37" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="14">
         <v>2016</v>
       </c>
       <c r="D37" s="1">
@@ -2549,10 +1919,10 @@
       </c>
     </row>
     <row r="38" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="14">
         <v>2016</v>
       </c>
       <c r="D38" s="1">
@@ -2584,10 +1954,10 @@
       </c>
     </row>
     <row r="39" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="14">
         <v>2016</v>
       </c>
       <c r="D39" s="1">
@@ -2619,10 +1989,10 @@
       </c>
     </row>
     <row r="40" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="14">
         <v>2015</v>
       </c>
       <c r="D40" s="1">
@@ -2654,10 +2024,10 @@
       </c>
     </row>
     <row r="41" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="14">
         <v>2015</v>
       </c>
       <c r="D41" s="1">
@@ -2689,10 +2059,10 @@
       </c>
     </row>
     <row r="42" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="14">
         <v>2015</v>
       </c>
       <c r="D42" s="1">
@@ -2724,10 +2094,10 @@
       </c>
     </row>
     <row r="43" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="14">
         <v>2014</v>
       </c>
       <c r="D43" s="1">
@@ -2759,10 +2129,10 @@
       </c>
     </row>
     <row r="44" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="14">
         <v>2014</v>
       </c>
       <c r="D44" s="1">
@@ -2794,10 +2164,10 @@
       </c>
     </row>
     <row r="45" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="14">
         <v>2014</v>
       </c>
       <c r="D45" s="1">
@@ -2829,10 +2199,10 @@
       </c>
     </row>
     <row r="46" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="14">
         <v>2013</v>
       </c>
       <c r="D46" s="1">
@@ -2864,10 +2234,10 @@
       </c>
     </row>
     <row r="47" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="14">
         <v>2013</v>
       </c>
       <c r="D47" s="1">
@@ -2899,10 +2269,10 @@
       </c>
     </row>
     <row r="48" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="14">
         <v>2013</v>
       </c>
       <c r="D48" s="1">
@@ -2934,10 +2304,10 @@
       </c>
     </row>
     <row r="49" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="14">
         <v>2012</v>
       </c>
       <c r="D49" s="1">
@@ -2969,10 +2339,10 @@
       </c>
     </row>
     <row r="50" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="14">
         <v>2012</v>
       </c>
       <c r="D50" s="1">
@@ -3004,10 +2374,10 @@
       </c>
     </row>
     <row r="51" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="14">
         <v>2012</v>
       </c>
       <c r="D51" s="1">
@@ -3039,10 +2409,10 @@
       </c>
     </row>
     <row r="52" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="14">
         <v>2011</v>
       </c>
       <c r="D52" s="1">
@@ -3074,10 +2444,10 @@
       </c>
     </row>
     <row r="53" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="14">
         <v>2011</v>
       </c>
       <c r="D53" s="1">
@@ -3109,10 +2479,10 @@
       </c>
     </row>
     <row r="54" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="14">
         <v>2011</v>
       </c>
       <c r="D54" s="1">
@@ -3144,107 +2514,107 @@
       </c>
     </row>
     <row r="55" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="14">
         <v>2005</v>
       </c>
-      <c r="D55" s="33">
+      <c r="D55" s="16">
         <v>24.154445420999647</v>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="16">
         <v>22.719256399342001</v>
       </c>
-      <c r="F55" s="33">
+      <c r="F55" s="16">
         <v>25.605238235645007</v>
       </c>
-      <c r="G55" s="33">
+      <c r="G55" s="16">
         <v>46.854783333813693</v>
       </c>
-      <c r="H55" s="33">
+      <c r="H55" s="16">
         <v>44.052614648999509</v>
       </c>
-      <c r="I55" s="33">
+      <c r="I55" s="16">
         <v>49.656039210780335</v>
       </c>
-      <c r="J55" s="33">
+      <c r="J55" s="16">
         <v>17.627766561885203</v>
       </c>
-      <c r="K55" s="33">
+      <c r="K55" s="16">
         <v>16.629289494749859</v>
       </c>
-      <c r="L55" s="33">
+      <c r="L55" s="16">
         <v>18.640340941561153</v>
       </c>
     </row>
     <row r="56" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="30" t="s">
+      <c r="B56" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="15">
         <v>2005</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="16">
         <v>58.914561886160612</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="16">
         <v>59.518557467873897</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="16">
         <v>58.303993447658122</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="16">
         <v>41.525124849172229</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="16">
         <v>45.554934551604795</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="16">
         <v>37.49662785926138</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="16">
         <v>63.914275570680147</v>
       </c>
-      <c r="K56" s="33">
+      <c r="K56" s="16">
         <v>63.504708417191956</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="16">
         <v>64.329620974211139</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="14">
         <v>2005</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="16">
         <v>16.930992692839745</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="16">
         <v>17.762186132784088</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="16">
         <v>16.090768316696874</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="16">
         <v>11.620091817014073</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="16">
         <v>10.392450799395696</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="16">
         <v>12.847332929958288</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="16">
         <v>18.457957867434651</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="16">
         <v>19.866002088058185</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="16">
         <v>17.030038084227709</v>
       </c>
     </row>
@@ -3260,125 +2630,125 @@
       <c r="J58" s="7"/>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B59" s="34" t="s">
+      <c r="B59" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="35"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21"/>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
-      <c r="K63" s="37"/>
-      <c r="L63" s="37"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
-      <c r="J64" s="37"/>
-      <c r="K64" s="37"/>
-      <c r="L64" s="37"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B65" s="37" t="s">
+      <c r="B65" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
-      <c r="K65" s="37"/>
-      <c r="L65" s="37"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B67" s="38" t="s">
+      <c r="B67" s="20" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B68" s="38" t="s">
+      <c r="B68" s="20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B69" s="38" t="s">
+      <c r="B69" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="18" t="s">
         <v>23</v>
       </c>
     </row>

--- a/assets/excel/2026_4-2-1.xlsx
+++ b/assets/excel/2026_4-2-1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BiesterChristophLSN\Desktop\MZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DF893-DAF0-4388-BFEE-23BEC2D2D38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63AD10E6-93E3-4FC0-8073-754727767A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F00CF707-31DB-41A0-9AE6-C8AE49075CB7}"/>
+    <workbookView xWindow="20052" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F00CF707-31DB-41A0-9AE6-C8AE49075CB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -135,9 +135,6 @@
     <t>1) Kein/noch kein beruflicher Abschluss vorhanden; einschließlich Anlernausbildung, Berufsvorbereitungsjahr und beruflichem Praktikum.</t>
   </si>
   <si>
-    <t xml:space="preserve">2) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
-  </si>
-  <si>
     <t>3) Seit dem Jahr 2018 wird im Mikrozensus der Migrationshintergrund im weiteren Sinne jährlich berichtet. Die in der Tabelle ab dem Jahr 2018 abgebildeten Daten zum Migrationshintergrund entsprechen dem Migrationshintergrund im weiteren Sinne, bis 2017 wird der Migrationshintergrund im engeren Sinne abgebildet. Die Vergleichbarkeit ist dadurch eingeschränkt.</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
   </si>
   <si>
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
+  </si>
+  <si>
+    <t>2) Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
   </si>
 </sst>
 </file>
@@ -548,9 +548,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -588,7 +588,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -694,7 +694,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -836,7 +836,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -855,7 +855,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2644,9 +2644,9 @@
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="21" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
@@ -2674,9 +2674,9 @@
       <c r="K61" s="21"/>
       <c r="L61" s="21"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
@@ -2689,9 +2689,9 @@
       <c r="K62" s="21"/>
       <c r="L62" s="21"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
@@ -2704,7 +2704,7 @@
       <c r="K63" s="19"/>
       <c r="L63" s="19"/>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
@@ -2717,9 +2717,9 @@
       <c r="K64" s="19"/>
       <c r="L64" s="19"/>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -2732,24 +2732,25 @@
       <c r="K65" s="19"/>
       <c r="L65" s="19"/>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B68" s="20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B69" s="20" t="s">
+    <row r="70" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="18" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B70" s="18" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
